--- a/output/extracted.xlsx
+++ b/output/extracted.xlsx
@@ -1236,6 +1236,9 @@
           <t>TOTALS</t>
         </is>
       </c>
+      <c r="O9" t="n">
+        <v>94</v>
+      </c>
       <c r="P9" t="n">
         <v>32</v>
       </c>
@@ -1256,7 +1259,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>TOTALS; grand_total_hours='#VALUE!'</t>
+          <t>TOTALS; Total Hours computed (BB9='#VALUE!')</t>
         </is>
       </c>
     </row>
@@ -2566,6 +2569,9 @@
           <t>TOTALS</t>
         </is>
       </c>
+      <c r="O25" t="n">
+        <v>95</v>
+      </c>
       <c r="P25" t="n">
         <v>32</v>
       </c>
@@ -2586,7 +2592,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>TOTALS; grand_total_hours='#VALUE!'</t>
+          <t>TOTALS; Total Hours computed (BB9='#VALUE!')</t>
         </is>
       </c>
     </row>
@@ -7483,8 +7489,8 @@
       <c r="W2" t="n">
         <v>94</v>
       </c>
-      <c r="X2" t="e">
-        <v>#VALUE!</v>
+      <c r="X2" t="n">
+        <v>94</v>
       </c>
       <c r="Y2" s="7" t="inlineStr">
         <is>
@@ -7687,8 +7693,8 @@
       <c r="W4" t="n">
         <v>95</v>
       </c>
-      <c r="X4" t="e">
-        <v>#VALUE!</v>
+      <c r="X4" t="n">
+        <v>95</v>
       </c>
       <c r="Y4" s="7" t="inlineStr">
         <is>
@@ -8499,7 +8505,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-21 02:22:54</t>
+          <t>2026-05-21 15:57:28</t>
         </is>
       </c>
       <c r="E2" t="n">

--- a/output/extracted.xlsx
+++ b/output/extracted.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>total_hrs='#VALUE!'</t>
+          <t>Start cell L5 = 'OFF' — not a time</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>TOTALS; Total Hours computed (BB9='#VALUE!')</t>
+          <t>Total Hours cell BB9 = '#VALUE!' — recomputed from day rows</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="X17" s="4" t="inlineStr">
         <is>
-          <t>TOTALS</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>total_hrs='#VALUE!'</t>
+          <t>Start cell L5 = 'OFF' — not a time</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>TOTALS; Total Hours computed (BB9='#VALUE!')</t>
+          <t>Total Hours cell BB9 = '#VALUE!' — recomputed from day rows</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="X33" s="4" t="inlineStr">
         <is>
-          <t>TOTALS</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="X41" s="4" t="inlineStr">
         <is>
-          <t>TOTALS</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="X49" s="4" t="inlineStr">
         <is>
-          <t>TOTALS</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="X57" s="4" t="inlineStr">
         <is>
-          <t>TOTALS</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="X65" s="4" t="inlineStr">
         <is>
-          <t>TOTALS</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="X73" s="4" t="inlineStr">
         <is>
-          <t>TOTALS</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="X81" s="4" t="inlineStr">
         <is>
-          <t>TOTALS</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -8505,7 +8505,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:57:28</t>
+          <t>2026-05-21 15:58:13</t>
         </is>
       </c>
       <c r="E2" t="n">
